--- a/survey_templates/021_pet_product_marketing_effectiveness_survey--survey_templates.xlsx
+++ b/survey_templates/021_pet_product_marketing_effectiveness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -574,14 +574,10 @@
           <t>Pet Age</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Enter pet's age in years</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -624,11 +620,7 @@
           <t>Customer Awareness</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Measure customer awareness on a 1-10 scale</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -791,305 +783,6 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>customer_awareness_10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Customer Awareness 10</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>referral_awareness</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>referral_awareness</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>customer_awareness_100</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Customer Awareness 100</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>customer_awareness_100</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Customer Awareness 100</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Customer Referral Amount 100</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>customer_awareness_scale_100</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Customer Awareness Scale 100</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_awareness_100</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Customer Awareness 100</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>customer_awareness_scale_100</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Customer Awareness Scale 100</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_scale</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Customer Awareness 100</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_scale</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Customer Referral Amount 100</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>customer_awareness_scale_100_scale</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Customer Awareness Scale 100</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_100</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Customer Awareness 100 100</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_100</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Customer Referral Amount 100 100</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1106,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1241,29 +934,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>marketing_channels_choices</t>
+          <t>referral_intent_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>online_advertising</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Online Advertising</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1275,46 +968,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>referral_intent_choices</t>
+          <t>customer_awareness_scale_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>referral_intent_choices</t>
+          <t>customer_awareness_scale_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1326,656 +1019,112 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>customer_awareness_scale_choices</t>
+          <t>referral_source_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>customer_awareness_scale_choices</t>
+          <t>referral_source_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>customer_awareness_scale_choices</t>
+          <t>referral_source_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>customer_awareness_scale_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>customer_awareness_scale_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>customer_awareness_scale_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>customer_awareness_scale_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>customer_awareness_scale_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>customer_awareness_scale_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>referral_source_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Social Media</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>referral_source_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>referral_source_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>online_advertising</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Online Advertising</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>referral_awareness_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Social Media</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>referral_awareness_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Not Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Not Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Not Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_scale_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_scale_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_scale_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Not Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_scale_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_scale_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_scale_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Not Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_100_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_100_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>customer_awareness_100_100_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Not Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_100_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Very Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_100_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>customer_referral_amount_100_100_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
         <is>
           <t>Not Satisfied</t>
         </is>
